--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -476,12 +476,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -608,7 +623,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -620,34 +635,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,7 +747,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,7 +766,19 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1303,31 +1330,31 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1338,34 +1365,34 @@
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="10" t="s">
         <v>23</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27045" windowHeight="11850"/>
+    <workbookView windowWidth="27285" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>单据编号</t>
   </si>
@@ -35,12 +35,18 @@
     <t>状态</t>
   </si>
   <si>
+    <t>同步平台</t>
+  </si>
+  <si>
+    <t>同步状态</t>
+  </si>
+  <si>
+    <t>同步单号</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
-    <t>图片</t>
-  </si>
-  <si>
     <t>sku</t>
   </si>
   <si>
@@ -59,10 +65,19 @@
     <t>调入虚拟仓</t>
   </si>
   <si>
-    <t>同步平台</t>
-  </si>
-  <si>
-    <t>同步单号</t>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>修改人</t>
+  </si>
+  <si>
+    <t>修改时间</t>
   </si>
   <si>
     <t>{.code}</t>
@@ -71,12 +86,18 @@
     <t>{.statusName}</t>
   </si>
   <si>
+    <t>{.sysTypeNames}</t>
+  </si>
+  <si>
+    <t>{.syncTypeName}</t>
+  </si>
+  <si>
+    <t>{.thirdCodes}</t>
+  </si>
+  <si>
     <t>{.typeName}</t>
   </si>
   <si>
-    <t>{.imageUrl}</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -95,10 +116,16 @@
     <t>{.toVirtualWarehouseName}</t>
   </si>
   <si>
-    <t>{.sysTypeNames}</t>
-  </si>
-  <si>
-    <t>{.thirdCodes}</t>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -747,7 +774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -760,25 +787,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1306,94 +1324,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="25.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="26.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="20.875" customWidth="1"/>
-    <col min="9" max="12" width="20" customWidth="1"/>
+    <col min="2" max="5" width="19.75" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="21.375" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="20.875" customWidth="1"/>
+    <col min="11" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="13.25" customWidth="1"/>
+    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
+    <col min="18" max="18" width="14.375" customWidth="1"/>
+    <col min="19" max="19" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="10" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:19">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="G2" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27285" windowHeight="11775"/>
+    <workbookView windowWidth="27285" windowHeight="8685"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>单据编号</t>
   </si>
@@ -1324,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1334,15 +1334,15 @@
     <col min="8" max="8" width="21.375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="20.875" customWidth="1"/>
-    <col min="11" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="13.25" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
-    <col min="17" max="17" width="14.5" customWidth="1"/>
-    <col min="18" max="18" width="14.375" customWidth="1"/>
-    <col min="19" max="19" width="11.875" customWidth="1"/>
+    <col min="11" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="13.25" customWidth="1"/>
+    <col min="14" max="14" width="16.125" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16" width="14.375" customWidth="1"/>
+    <col min="17" max="17" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1380,28 +1380,22 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:19">
+    <row r="2" s="2" customFormat="1" spans="1:17">
       <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
@@ -1439,22 +1433,16 @@
         <v>28</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="P2" s="6"/>
       <c r="Q2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6" t="s">
         <v>32</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -86,13 +86,13 @@
     <t>{.statusName}</t>
   </si>
   <si>
-    <t>{.sysTypeNames}</t>
-  </si>
-  <si>
-    <t>{.syncTypeName}</t>
-  </si>
-  <si>
-    <t>{.thirdCodes}</t>
+    <t>{.sysTypeName}</t>
+  </si>
+  <si>
+    <t>{.syncStatusName}</t>
+  </si>
+  <si>
+    <t>{.thirdCode}</t>
   </si>
   <si>
     <t>{.typeName}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>单据编号</t>
   </si>
@@ -122,7 +122,10 @@
     <t>{.createUserName}</t>
   </si>
   <si>
-    <t>{.createTime}{.updateUserName}</t>
+    <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.updateUserName}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
@@ -1336,10 +1339,10 @@
     <col min="10" max="10" width="20.875" customWidth="1"/>
     <col min="11" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="13.25" customWidth="1"/>
-    <col min="14" max="14" width="16.125" customWidth="1"/>
-    <col min="15" max="15" width="14.5" customWidth="1"/>
-    <col min="16" max="16" width="14.375" customWidth="1"/>
-    <col min="17" max="17" width="11.875" customWidth="1"/>
+    <col min="14" max="14" width="18.25" customWidth="1"/>
+    <col min="15" max="15" width="16.125" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
@@ -1441,9 +1444,11 @@
       <c r="O2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="6"/>
+      <c r="P2" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="Q2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27285" windowHeight="8685"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>单据编号</t>
   </si>
@@ -65,7 +65,10 @@
     <t>调入虚拟仓</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>订单备注</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
   <si>
     <t>创建人</t>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1327,7 +1333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1338,14 +1344,15 @@
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="20.875" customWidth="1"/>
     <col min="11" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="13.25" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="16.125" customWidth="1"/>
-    <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="17.25" customWidth="1"/>
+    <col min="14" max="14" width="18.75" customWidth="1"/>
+    <col min="15" max="15" width="18.25" customWidth="1"/>
+    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="17" max="17" width="13.5" customWidth="1"/>
+    <col min="18" max="18" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1397,58 +1404,64 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
+    <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>单据编号</t>
   </si>
@@ -56,15 +56,24 @@
     <t>实体仓</t>
   </si>
   <si>
+    <t>实体仓可分配数量</t>
+  </si>
+  <si>
     <t>调出虚拟仓</t>
   </si>
   <si>
+    <t>调出仓可用数</t>
+  </si>
+  <si>
+    <t>调入虚拟仓</t>
+  </si>
+  <si>
+    <t>调入仓可用数</t>
+  </si>
+  <si>
     <t>分配/变更/取消数量</t>
   </si>
   <si>
-    <t>调入虚拟仓</t>
-  </si>
-  <si>
     <t>订单备注</t>
   </si>
   <si>
@@ -110,13 +119,19 @@
     <t>{.warehouseName}</t>
   </si>
   <si>
+    <t>{.unDistributionQty}</t>
+  </si>
+  <si>
     <t>{.fromVirtualWarehouseName}</t>
   </si>
   <si>
+    <t>{.fromVirtualWarehouseUsableQty}</t>
+  </si>
+  <si>
+    <t>{.toVirtualWarehouseName}</t>
+  </si>
+  <si>
     <t>{.qty}</t>
-  </si>
-  <si>
-    <t>{.toVirtualWarehouseName}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1333,7 +1348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
@@ -1342,17 +1357,21 @@
     <col min="7" max="7" width="16.875" customWidth="1"/>
     <col min="8" max="8" width="21.375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="20.875" customWidth="1"/>
-    <col min="11" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="18.75" customWidth="1"/>
-    <col min="15" max="15" width="18.25" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="19.375" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="20.875" customWidth="1"/>
+    <col min="12" max="12" width="22.75" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="17" max="17" width="18.75" customWidth="1"/>
+    <col min="18" max="18" width="18.25" customWidth="1"/>
+    <col min="19" max="19" width="16.125" customWidth="1"/>
+    <col min="20" max="20" width="13.5" customWidth="1"/>
+    <col min="21" max="21" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1407,61 +1426,79 @@
       <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:18">
+    <row r="2" s="2" customFormat="1" spans="1:21">
       <c r="A2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/VirtualWarehouseAllocation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>单据编号</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>{.toVirtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.toVirtualWarehouseUsableQty}</t>
   </si>
   <si>
     <t>{.qty}</t>
@@ -1477,28 +1480,28 @@
         <v>33</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
